--- a/banking_forms/001_small_business_credit_application_form--banking_forms.xlsx
+++ b/banking_forms/001_small_business_credit_application_form--banking_forms.xlsx
@@ -1,15 +1,15 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="survey" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="choices" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="settings" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="survey" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="choices" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="settings" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -1102,8 +1102,8 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="28" customWidth="1" min="1" max="1"/>
-    <col width="50" customWidth="1" min="2" max="2"/>
-    <col width="50" customWidth="1" min="3" max="3"/>
+    <col width="21" customWidth="1" min="2" max="2"/>
+    <col width="21" customWidth="1" min="3" max="3"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -1131,12 +1131,12 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>{'id':_'credit_score',_'label':_'excellent',_'value':_850}</t>
+          <t>excellent</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>{'id': 'credit_score', 'label': 'Excellent', 'value': 850}</t>
+          <t>Excellent</t>
         </is>
       </c>
     </row>
@@ -1148,12 +1148,12 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>{'id':_'credit_score',_'label':_'good',_'value':_720}</t>
+          <t>good</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>{'id': 'credit_score', 'label': 'Good', 'value': 720}</t>
+          <t>Good</t>
         </is>
       </c>
     </row>
@@ -1165,12 +1165,12 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>{'id':_'credit_score',_'label':_'fair',_'value':_680}</t>
+          <t>fair</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>{'id': 'credit_score', 'label': 'Fair', 'value': 680}</t>
+          <t>Fair</t>
         </is>
       </c>
     </row>
@@ -1182,12 +1182,12 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>{'id':_'owner_type',_'label':_'sole_proprietor',_'value':_1}</t>
+          <t>sole_proprietor</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>{'id': 'owner_type', 'label': 'Sole Proprietor', 'value': 1}</t>
+          <t>Sole Proprietor</t>
         </is>
       </c>
     </row>
@@ -1199,12 +1199,12 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>{'id':_'owner_type',_'label':_'partnership',_'value':_2}</t>
+          <t>partnership</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>{'id': 'owner_type', 'label': 'Partnership', 'value': 2}</t>
+          <t>Partnership</t>
         </is>
       </c>
     </row>
@@ -1216,12 +1216,12 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>{'id':_'owner_type',_'label':_'corporation',_'value':_3}</t>
+          <t>corporation</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>{'id': 'owner_type', 'label': 'Corporation', 'value': 3}</t>
+          <t>Corporation</t>
         </is>
       </c>
     </row>
@@ -1233,12 +1233,12 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>{'id':_'sole_proprietorship',_'label':_'sole_proprietorship',_'value':_1}</t>
+          <t>sole_proprietorship</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>{'id': 'sole_proprietorship', 'label': 'Sole Proprietorship', 'value': 1}</t>
+          <t>Sole Proprietorship</t>
         </is>
       </c>
     </row>
@@ -1250,12 +1250,12 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>{'id':_'single_member_llc',_'label':_'single_member_llc',_'value':_2}</t>
+          <t>single_member_llc</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>{'id': 'single_member_llc', 'label': 'Single Member LLC', 'value': 2}</t>
+          <t>Single Member LLC</t>
         </is>
       </c>
     </row>
@@ -1267,12 +1267,12 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>{'id':_'multi_member_llc',_'label':_'multi-member_llc',_'value':_3}</t>
+          <t>multi-member_llc</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>{'id': 'multi_member_llc', 'label': 'Multi-Member LLC', 'value': 3}</t>
+          <t>Multi-Member LLC</t>
         </is>
       </c>
     </row>
@@ -1284,12 +1284,12 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>{'id':_'no_license',_'label':_'no_license',_'value':_1}</t>
+          <t>no_license</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>{'id': 'no_license', 'label': 'No License', 'value': 1}</t>
+          <t>No License</t>
         </is>
       </c>
     </row>
@@ -1301,12 +1301,12 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>{'id':_'valid_license',_'label':_'valid_license',_'value':_2}</t>
+          <t>valid_license</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>{'id': 'valid_license', 'label': 'Valid License', 'value': 2}</t>
+          <t>Valid License</t>
         </is>
       </c>
     </row>
@@ -1318,12 +1318,12 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>{'id':_'expired_license',_'label':_'expired_license',_'value':_3}</t>
+          <t>expired_license</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>{'id': 'expired_license', 'label': 'Expired License', 'value': 3}</t>
+          <t>Expired License</t>
         </is>
       </c>
     </row>
@@ -1335,12 +1335,12 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>{'id':_'pending_approval',_'label':_'pending_approval',_'value':_1}</t>
+          <t>pending_approval</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>{'id': 'pending_approval', 'label': 'Pending Approval', 'value': 1}</t>
+          <t>Pending Approval</t>
         </is>
       </c>
     </row>
@@ -1352,12 +1352,12 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>{'id':_'approved',_'label':_'approved',_'value':_2}</t>
+          <t>approved</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>{'id': 'approved', 'label': 'Approved', 'value': 2}</t>
+          <t>Approved</t>
         </is>
       </c>
     </row>
@@ -1369,12 +1369,12 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>{'id':_'denied',_'label':_'denied',_'value':_3}</t>
+          <t>denied</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>{'id': 'denied', 'label': 'Denied', 'value': 3}</t>
+          <t>Denied</t>
         </is>
       </c>
     </row>
@@ -1386,12 +1386,12 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>{'id':_'loan_officer',_'label':_'loan_officer',_'value':_1}</t>
+          <t>loan_officer</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>{'id': 'loan_officer', 'label': 'Loan Officer', 'value': 1}</t>
+          <t>Loan Officer</t>
         </is>
       </c>
     </row>
@@ -1403,12 +1403,12 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>{'id':_'credit_manager',_'label':_'credit_manager',_'value':_2}</t>
+          <t>credit_manager</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>{'id': 'credit_manager', 'label': 'Credit Manager', 'value': 2}</t>
+          <t>Credit Manager</t>
         </is>
       </c>
     </row>
@@ -1420,12 +1420,12 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>{'id':_'approved_loan',_'label':_'approved_loan',_'value':_1}</t>
+          <t>approved_loan</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>{'id': 'approved_loan', 'label': 'Approved Loan', 'value': 1}</t>
+          <t>Approved Loan</t>
         </is>
       </c>
     </row>
@@ -1437,12 +1437,12 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>{'id':_'rejected_loan',_'label':_'rejected_loan',_'value':_2}</t>
+          <t>rejected_loan</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>{'id': 'rejected_loan', 'label': 'Rejected Loan', 'value': 2}</t>
+          <t>Rejected Loan</t>
         </is>
       </c>
     </row>
